--- a/00-Administratif/01-ETIQUETTES + NOMBRE  NOTES SEMESTRIELLES/PELE/CONTROLE NOMBRE DE NOTES PELE 2.xlsx
+++ b/00-Administratif/01-ETIQUETTES + NOMBRE  NOTES SEMESTRIELLES/PELE/CONTROLE NOMBRE DE NOTES PELE 2.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4507"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29022"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_11B4D7B5368357818918F4FEAC97133E255B9C75" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PELE 2" sheetId="7" r:id="rId1"/>
@@ -12,6 +13,9 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -28,16 +32,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="19">
   <si>
+    <t>NOMBRE DE NOTES AU MINIMUM A INTRODUIRE PELE 2</t>
+  </si>
+  <si>
     <t>DOMAINE DE COMPETENCE</t>
   </si>
   <si>
     <t>DISCIPLINES</t>
-  </si>
-  <si>
-    <t>BTE</t>
-  </si>
-  <si>
-    <t>Electrotechnique</t>
   </si>
   <si>
     <r>
@@ -68,9 +69,24 @@
     </r>
   </si>
   <si>
+    <t>BTE</t>
+  </si>
+  <si>
+    <t>Electrotechnique</t>
+  </si>
+  <si>
+    <t>Physique</t>
+  </si>
+  <si>
     <t>DTE</t>
   </si>
   <si>
+    <t>NIBT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schémas </t>
+  </si>
+  <si>
     <t>Culture générale</t>
   </si>
   <si>
@@ -78,18 +94,6 @@
   </si>
   <si>
     <t>Société</t>
-  </si>
-  <si>
-    <t>Physique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schémas </t>
-  </si>
-  <si>
-    <t>NOMBRE DE NOTES AU MINIMUM A INTRODUIRE PELE 2</t>
-  </si>
-  <si>
-    <t>NIBT</t>
   </si>
   <si>
     <t>NOMBRE DE NOTES AU MINIMUM A INTRODUIRE PELE 2 ++</t>
@@ -110,7 +114,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -458,6 +462,12 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -465,12 +475,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -500,9 +504,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -540,7 +544,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -574,6 +578,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -608,9 +613,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -783,9 +789,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:J22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="25.28515625" defaultRowHeight="27.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="25.28515625" defaultRowHeight="27.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="38.5703125" style="2" customWidth="1"/>
     <col min="2" max="2" width="24.42578125" style="2" customWidth="1"/>
@@ -800,17 +806,17 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10" ht="36.950000000000003" customHeight="1">
-      <c r="A2" s="54" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
+      <c r="A2" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
       <c r="J2" s="2"/>
     </row>
     <row r="3" spans="1:10" ht="27.95" customHeight="1">
@@ -824,22 +830,22 @@
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="48.75" customHeight="1">
       <c r="A4" s="41" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B4" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="51" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="53" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="54"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="52"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="51" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="52"/>
-      <c r="I4" s="53"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="55"/>
     </row>
     <row r="5" spans="1:10" s="14" customFormat="1" ht="14.25">
       <c r="A5" s="8"/>
@@ -855,7 +861,7 @@
     </row>
     <row r="6" spans="1:10" s="25" customFormat="1" ht="24.95" customHeight="1">
       <c r="A6" s="26" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B6" s="21"/>
       <c r="C6" s="22"/>
@@ -870,7 +876,7 @@
     <row r="7" spans="1:10" s="14" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A7" s="15"/>
       <c r="B7" s="27" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C7" s="4">
         <v>1</v>
@@ -896,7 +902,7 @@
     <row r="8" spans="1:10" s="14" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A8" s="15"/>
       <c r="B8" s="27" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C8" s="4">
         <v>1</v>
@@ -931,7 +937,7 @@
     </row>
     <row r="10" spans="1:10" s="25" customFormat="1" ht="24.95" customHeight="1">
       <c r="A10" s="26" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B10" s="21"/>
       <c r="C10" s="22"/>
@@ -946,7 +952,7 @@
     <row r="11" spans="1:10" s="14" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A11" s="15"/>
       <c r="B11" s="49" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C11" s="4">
         <v>1</v>
@@ -970,7 +976,7 @@
     <row r="12" spans="1:10" s="14" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A12" s="15"/>
       <c r="B12" s="49" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" s="4">
         <v>1</v>
@@ -1005,7 +1011,7 @@
     </row>
     <row r="14" spans="1:10" s="25" customFormat="1" ht="24.95" customHeight="1">
       <c r="A14" s="26" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B14" s="21"/>
       <c r="C14" s="22"/>
@@ -1020,7 +1026,7 @@
     <row r="15" spans="1:10" s="14" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A15" s="15"/>
       <c r="B15" s="27" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C15" s="4">
         <v>1</v>
@@ -1046,7 +1052,7 @@
     <row r="16" spans="1:10" s="14" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A16" s="15"/>
       <c r="B16" s="27" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C16" s="4">
         <v>1</v>
@@ -1148,9 +1154,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:J21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="25.28515625" defaultRowHeight="27.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="25.28515625" defaultRowHeight="27.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="38.5703125" style="2" customWidth="1"/>
     <col min="2" max="2" width="25.42578125" style="2" customWidth="1"/>
@@ -1165,17 +1171,17 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10" ht="36.950000000000003" customHeight="1">
-      <c r="A2" s="54" t="s">
+      <c r="A2" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
       <c r="J2" s="2"/>
     </row>
     <row r="3" spans="1:10" ht="27.95" customHeight="1">
@@ -1189,22 +1195,22 @@
     </row>
     <row r="4" spans="1:10" s="7" customFormat="1" ht="48" customHeight="1">
       <c r="A4" s="41" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B4" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="51" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="53" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="54"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="52"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="51" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="52"/>
-      <c r="I4" s="53"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="55"/>
     </row>
     <row r="5" spans="1:10" s="14" customFormat="1" ht="14.25">
       <c r="A5" s="8"/>
@@ -1220,7 +1226,7 @@
     </row>
     <row r="6" spans="1:10" s="25" customFormat="1" ht="24.95" customHeight="1">
       <c r="A6" s="26" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B6" s="21"/>
       <c r="C6" s="22"/>
@@ -1257,7 +1263,7 @@
     <row r="8" spans="1:10" s="14" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A8" s="15"/>
       <c r="B8" s="49" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C8" s="4">
         <v>1</v>
@@ -1334,7 +1340,7 @@
     </row>
     <row r="12" spans="1:10" s="25" customFormat="1" ht="24.95" customHeight="1">
       <c r="A12" s="26" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -1471,6 +1477,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="81e70d26-bf48-4cf6-8ac1-a02ba5208bf1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="28ecda99-baeb-4159-826c-8d3ebe501c98" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F7262808F74C1A479C3BB44A303B6A0F" ma:contentTypeVersion="16" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="53ca5ba934d9ea82b208c5ebaa87ee73">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="81e70d26-bf48-4cf6-8ac1-a02ba5208bf1" xmlns:ns3="28ecda99-baeb-4159-826c-8d3ebe501c98" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="61005504990099e8d9d64d1794496304" ns2:_="" ns3:_="">
     <xsd:import namespace="81e70d26-bf48-4cf6-8ac1-a02ba5208bf1"/>
@@ -1705,28 +1731,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="81e70d26-bf48-4cf6-8ac1-a02ba5208bf1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="28ecda99-baeb-4159-826c-8d3ebe501c98" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8F315E9-665E-4B08-88A7-90B06A7C11AE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE3A8F6F-B7ED-437F-8A2E-2645E833B9E3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1734,5 +1740,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE3A8F6F-B7ED-437F-8A2E-2645E833B9E3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8F315E9-665E-4B08-88A7-90B06A7C11AE}"/>
 </file>